--- a/data/trans_orig/IQ19A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ19A-Edad-trans_orig.xlsx
@@ -2886,7 +2886,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -3512,12 +3512,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17700</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -3845,12 +3845,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>51310</t>
+          <t>50917</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>40745</t>
+          <t>41010</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>49215</t>
+          <t>48970</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>86203</t>
+          <t>86442</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>98397</t>
+          <t>98730</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4961,12 +4961,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>722</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>12193</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5046,12 +5046,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -5405,12 +5405,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>12547</t>
+          <t>13166</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5420,12 +5420,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>16637</t>
+          <t>16035</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>29805</t>
+          <t>29289</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5490,12 +5490,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -5516,12 +5516,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>41338</t>
+          <t>41077</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>53517</t>
+          <t>53600</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>41899</t>
+          <t>42374</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>54262</t>
+          <t>54884</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>87749</t>
+          <t>88279</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>105160</t>
+          <t>104881</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,74%</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>531</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -6632,12 +6632,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>22053</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6647,12 +6647,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6667,12 +6667,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>23936</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>24219</t>
+          <t>24905</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>40833</t>
+          <t>41677</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -6854,12 +6854,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>7808</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>11509</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>10925</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -7076,12 +7076,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>17911</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7091,12 +7091,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7111,12 +7111,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>22971</t>
+          <t>23073</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>46408</t>
+          <t>46315</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>61745</t>
+          <t>62169</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>54170</t>
+          <t>53346</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>67258</t>
+          <t>66960</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>104718</t>
+          <t>105209</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>125484</t>
+          <t>125357</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,19%</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -7899,7 +7899,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -8303,12 +8303,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>26864</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8338,12 +8338,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>13651</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>27879</t>
+          <t>27653</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8353,12 +8353,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8373,12 +8373,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>31109</t>
+          <t>30074</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>50594</t>
+          <t>49709</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>17057</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>839</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>21976</t>
+          <t>21498</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8610,12 +8610,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -8636,12 +8636,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8686,12 +8686,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8706,12 +8706,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>22599</t>
+          <t>22127</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -8747,12 +8747,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>18207</t>
+          <t>18784</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34436</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>33650</t>
+          <t>33067</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8797,12 +8797,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>40008</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>62895</t>
+          <t>61289</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -8858,12 +8858,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>138973</t>
+          <t>137678</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>161586</t>
+          <t>160312</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>144634</t>
+          <t>144746</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>166579</t>
+          <t>165683</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -8928,12 +8928,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>288920</t>
+          <t>290395</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>321299</t>
+          <t>319744</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -8943,12 +8943,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,13%</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -12104,7 +12104,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12169,12 +12169,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -12210,12 +12210,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>556</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12245,12 +12245,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12280,12 +12280,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -12321,12 +12321,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>13193</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12336,12 +12336,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12559</t>
+          <t>12194</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12406,12 +12406,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -12432,12 +12432,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>36777</t>
+          <t>36917</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>47421</t>
+          <t>46982</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>53281</t>
+          <t>53297</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>63578</t>
+          <t>63695</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12482,12 +12482,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>93614</t>
+          <t>93448</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>107807</t>
+          <t>107882</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12517,12 +12517,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -13331,7 +13331,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -13477,7 +13477,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -13548,12 +13548,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -13583,12 +13583,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>9384</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -13598,12 +13598,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -13618,12 +13618,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>15008</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -13633,12 +13633,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -13699,7 +13699,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -13749,7 +13749,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -13810,7 +13810,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -13881,12 +13881,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5378</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -13931,12 +13931,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -13992,12 +13992,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -14007,12 +14007,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -14027,12 +14027,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>9863</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>21966</t>
+          <t>21758</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -14042,12 +14042,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>20050</t>
+          <t>20007</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>36442</t>
+          <t>35186</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -14077,12 +14077,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -14103,12 +14103,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>49639</t>
+          <t>49583</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>63733</t>
+          <t>63686</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -14118,12 +14118,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -14138,12 +14138,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>40518</t>
+          <t>41273</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>53830</t>
+          <t>53858</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -14153,12 +14153,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>94153</t>
+          <t>94871</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>114391</t>
+          <t>114104</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,17%</t>
         </is>
       </c>
     </row>
@@ -14482,7 +14482,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14669,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -15002,7 +15002,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -15219,12 +15219,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>13960</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -15254,12 +15254,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>12618</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -15289,12 +15289,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>23332</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -15365,12 +15365,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>861</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -15380,12 +15380,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -15400,12 +15400,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -15415,12 +15415,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -15476,12 +15476,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>5245</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -15511,12 +15511,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -15526,12 +15526,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -15552,12 +15552,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -15567,12 +15567,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -15587,12 +15587,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -15602,12 +15602,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -15622,12 +15622,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>14253</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -15637,12 +15637,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -15663,12 +15663,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>10522</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>22789</t>
+          <t>22355</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -15678,12 +15678,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -15698,12 +15698,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>8819</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>19498</t>
+          <t>19638</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -15713,12 +15713,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -15733,12 +15733,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>38977</t>
+          <t>39171</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -15748,12 +15748,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -15774,12 +15774,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>37824</t>
+          <t>38289</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>52743</t>
+          <t>52439</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -15789,12 +15789,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -15809,12 +15809,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>34621</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>48193</t>
+          <t>48430</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -15824,12 +15824,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -15844,12 +15844,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>77370</t>
+          <t>76364</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>97619</t>
+          <t>97346</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -15859,12 +15859,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,26%</t>
         </is>
       </c>
     </row>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -16340,7 +16340,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -16375,7 +16375,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -16577,7 +16577,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -16743,7 +16743,7 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -16819,7 +16819,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -16869,7 +16869,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>20689</t>
+          <t>20430</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>19168</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>18980</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>35795</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -17001,12 +17001,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>440</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -17021,7 +17021,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -17036,12 +17036,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -17051,12 +17051,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -17071,12 +17071,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -17086,12 +17086,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -17147,12 +17147,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -17167,7 +17167,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -17182,12 +17182,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -17197,12 +17197,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -17223,12 +17223,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>21833</t>
+          <t>22292</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -17238,12 +17238,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -17258,12 +17258,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>10857</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -17273,12 +17273,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>14976</t>
+          <t>14936</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>30325</t>
+          <t>29181</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -17308,12 +17308,12 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -17334,12 +17334,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>27144</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>44829</t>
+          <t>45234</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -17349,12 +17349,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -17369,12 +17369,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>28341</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>45989</t>
+          <t>45122</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -17384,12 +17384,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -17404,12 +17404,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>60109</t>
+          <t>58887</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>86427</t>
+          <t>84994</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -17419,12 +17419,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -17445,12 +17445,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>134960</t>
+          <t>136364</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>157006</t>
+          <t>157964</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -17460,12 +17460,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -17480,12 +17480,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>137295</t>
+          <t>137334</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>158835</t>
+          <t>159036</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -17495,12 +17495,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -17515,12 +17515,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>278761</t>
+          <t>279017</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>310860</t>
+          <t>310932</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -17530,12 +17530,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,96%</t>
         </is>
       </c>
     </row>
@@ -20025,7 +20025,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -20040,7 +20040,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -20095,7 +20095,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -20110,7 +20110,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -20504,7 +20504,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -20539,7 +20539,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4657</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -20554,7 +20554,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -20595,7 +20595,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -20665,7 +20665,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -20706,7 +20706,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -20756,12 +20756,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>543</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -20771,12 +20771,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -20802,7 +20802,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -20817,7 +20817,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -20837,7 +20837,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -20872,7 +20872,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -20887,7 +20887,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -20908,12 +20908,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -20923,12 +20923,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -20943,12 +20943,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>11705</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -20958,12 +20958,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -20993,12 +20993,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -21019,12 +21019,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32396</t>
+          <t>32657</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>40928</t>
+          <t>40948</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -21034,12 +21034,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>38737</t>
+          <t>39490</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48686</t>
+          <t>48929</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -21069,12 +21069,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -21089,12 +21089,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>75147</t>
+          <t>74734</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>87836</t>
+          <t>87256</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -21104,12 +21104,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -22044,7 +22044,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -22099,7 +22099,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -22135,12 +22135,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -22150,12 +22150,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -22170,12 +22170,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -22190,7 +22190,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -22205,12 +22205,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>12802</t>
+          <t>12741</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -22220,12 +22220,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -22251,7 +22251,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -22266,7 +22266,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -22301,7 +22301,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -22336,7 +22336,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -22362,7 +22362,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -22377,7 +22377,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -22412,7 +22412,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -22427,12 +22427,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -22447,7 +22447,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -22468,12 +22468,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -22483,12 +22483,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -22503,12 +22503,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -22538,12 +22538,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -22553,12 +22553,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -22579,12 +22579,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>17452</t>
+          <t>16491</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -22594,12 +22594,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -22614,12 +22614,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -22629,12 +22629,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -22649,12 +22649,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>13020</t>
+          <t>13809</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>27966</t>
+          <t>27921</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -22664,12 +22664,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -22690,12 +22690,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>55418</t>
+          <t>55645</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>67891</t>
+          <t>68182</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -22705,12 +22705,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -22725,12 +22725,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>60535</t>
+          <t>61262</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>72627</t>
+          <t>73325</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -22740,12 +22740,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -22760,12 +22760,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>120816</t>
+          <t>119727</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>139010</t>
+          <t>137943</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -22775,12 +22775,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -23271,7 +23271,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -23291,7 +23291,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -23321,12 +23321,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -23806,12 +23806,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>14597</t>
+          <t>14005</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -23821,12 +23821,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -23841,12 +23841,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -23856,12 +23856,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -23876,12 +23876,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>17763</t>
+          <t>18254</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -23891,12 +23891,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -23922,7 +23922,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>5567</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -23937,7 +23937,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -23957,7 +23957,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -23987,12 +23987,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -24007,7 +24007,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -24033,7 +24033,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -24068,7 +24068,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -24083,7 +24083,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -24103,7 +24103,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -24139,12 +24139,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>15066</t>
+          <t>14494</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -24154,12 +24154,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -24179,7 +24179,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -24194,7 +24194,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -24209,12 +24209,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -24224,12 +24224,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>14882</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -24265,12 +24265,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -24285,12 +24285,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>14284</t>
+          <t>14236</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -24300,12 +24300,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -24320,12 +24320,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>12116</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>25611</t>
+          <t>25191</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -24361,12 +24361,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>45342</t>
+          <t>45986</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>59512</t>
+          <t>60200</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -24376,12 +24376,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -24396,12 +24396,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>45002</t>
+          <t>45148</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>57178</t>
+          <t>56789</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -24411,12 +24411,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -24431,12 +24431,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>95006</t>
+          <t>93923</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>113337</t>
+          <t>113765</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -24446,12 +24446,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -24927,7 +24927,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -24942,7 +24942,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -24962,7 +24962,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -24977,7 +24977,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -24992,12 +24992,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>10980</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -25007,12 +25007,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -25038,7 +25038,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -25053,7 +25053,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -25108,7 +25108,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -25371,7 +25371,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -25441,7 +25441,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -25456,7 +25456,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -25477,12 +25477,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>19775</t>
+          <t>19800</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -25492,12 +25492,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -25512,12 +25512,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -25527,12 +25527,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -25547,12 +25547,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>15057</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>29665</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -25562,12 +25562,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -25588,12 +25588,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>778</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -25603,12 +25603,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -25628,7 +25628,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -25643,7 +25643,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -25663,7 +25663,7 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -25678,7 +25678,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -25699,12 +25699,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -25719,7 +25719,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -25734,12 +25734,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>836</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -25749,12 +25749,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -25769,12 +25769,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -25784,12 +25784,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -25810,12 +25810,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>19681</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -25825,12 +25825,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -25845,12 +25845,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -25860,12 +25860,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -25880,12 +25880,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>25378</t>
+          <t>25066</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -25895,12 +25895,12 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -25921,12 +25921,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>18231</t>
+          <t>18831</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>34018</t>
+          <t>34384</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -25936,12 +25936,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -25956,12 +25956,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>33386</t>
+          <t>34116</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -25971,12 +25971,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -25991,12 +25991,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>40413</t>
+          <t>41207</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>62834</t>
+          <t>63630</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -26006,12 +26006,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -26032,12 +26032,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>142031</t>
+          <t>142223</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>163061</t>
+          <t>163865</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -26047,12 +26047,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -26067,12 +26067,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>154862</t>
+          <t>153565</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>172526</t>
+          <t>173392</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -26082,12 +26082,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -26102,12 +26102,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>301798</t>
+          <t>301996</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>330808</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -26117,12 +26117,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -27899,7 +27899,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -27914,7 +27914,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -28005,7 +28005,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -28020,7 +28020,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -29056,7 +29056,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -29071,7 +29071,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -29091,7 +29091,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -29106,7 +29106,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -29126,7 +29126,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -29141,7 +29141,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -29384,12 +29384,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>534</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -29399,12 +29399,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -29424,7 +29424,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -29439,7 +29439,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>7794</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -29469,12 +29469,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -29495,12 +29495,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -29510,12 +29510,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -29530,12 +29530,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>13124</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -29545,12 +29545,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -29565,12 +29565,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18380</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -29580,12 +29580,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -29606,12 +29606,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>24414</t>
+          <t>25160</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>32726</t>
+          <t>32414</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -29621,12 +29621,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -29641,12 +29641,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19971</t>
+          <t>20169</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>29461</t>
+          <t>29653</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -29656,12 +29656,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -29676,12 +29676,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>47603</t>
+          <t>47903</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>60320</t>
+          <t>60115</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -29691,12 +29691,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -30394,7 +30394,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -30409,7 +30409,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -30479,7 +30479,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -30722,12 +30722,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -30737,12 +30737,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -30762,7 +30762,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -30777,7 +30777,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -30792,12 +30792,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -30807,12 +30807,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -30838,7 +30838,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -30853,7 +30853,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -30873,7 +30873,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -30888,7 +30888,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -30903,12 +30903,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>426</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -30923,7 +30923,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -30949,7 +30949,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -30964,7 +30964,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -31019,7 +31019,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>4897</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -31034,7 +31034,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -31055,12 +31055,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8859</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -31070,12 +31070,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -31095,7 +31095,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -31125,12 +31125,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -31140,12 +31140,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -31166,12 +31166,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>456</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -31181,12 +31181,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -31201,12 +31201,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -31236,12 +31236,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>19017</t>
+          <t>20127</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -31251,12 +31251,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -31277,12 +31277,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>33211</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>44048</t>
+          <t>44097</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -31292,12 +31292,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -31312,12 +31312,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>67072</t>
+          <t>68567</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>80775</t>
+          <t>81146</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -31327,12 +31327,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -31347,12 +31347,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>106793</t>
+          <t>105674</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>122847</t>
+          <t>122346</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -31362,12 +31362,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,36%</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -31969,7 +31969,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -32024,7 +32024,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -32039,7 +32039,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -32322,7 +32322,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -32337,7 +32337,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -32357,7 +32357,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -32372,7 +32372,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -32393,12 +32393,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>7667</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>19388</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -32408,12 +32408,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -32428,12 +32428,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>14940</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -32443,12 +32443,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -32463,12 +32463,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>14440</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>29897</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -32478,12 +32478,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -32504,12 +32504,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -32519,12 +32519,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -32544,7 +32544,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -32559,7 +32559,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -32574,12 +32574,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -32589,12 +32589,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -32670,7 +32670,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -32690,7 +32690,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -32726,12 +32726,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -32741,12 +32741,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -32761,12 +32761,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -32776,12 +32776,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -32796,12 +32796,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>12189</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -32811,12 +32811,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -32837,12 +32837,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -32852,12 +32852,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -32872,12 +32872,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>15860</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -32887,12 +32887,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -32907,12 +32907,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>27569</t>
+          <t>26549</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -32922,12 +32922,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -32948,12 +32948,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>62302</t>
+          <t>62344</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>77408</t>
+          <t>77619</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -32963,12 +32963,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -32983,12 +32983,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>74070</t>
+          <t>74348</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>91907</t>
+          <t>92316</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -32998,12 +32998,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -33018,12 +33018,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>142261</t>
+          <t>141956</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>166713</t>
+          <t>166186</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -33033,12 +33033,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -33625,7 +33625,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -33640,7 +33640,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -33695,7 +33695,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -33710,7 +33710,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -33736,7 +33736,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -33751,7 +33751,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -33806,7 +33806,7 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -33821,7 +33821,7 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -33993,7 +33993,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -34028,7 +34028,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -34043,7 +34043,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -34064,12 +34064,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>25272</t>
+          <t>23937</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -34079,12 +34079,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -34099,12 +34099,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -34114,12 +34114,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -34134,12 +34134,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>19076</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>38408</t>
+          <t>37812</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -34149,12 +34149,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -34175,12 +34175,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -34190,12 +34190,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -34210,12 +34210,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>755</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -34225,12 +34225,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -34245,12 +34245,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -34260,12 +34260,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -34291,7 +34291,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -34306,7 +34306,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -34326,7 +34326,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -34341,7 +34341,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -34356,12 +34356,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -34371,12 +34371,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -34397,12 +34397,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -34412,12 +34412,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -34432,12 +34432,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>10563</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -34447,12 +34447,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -34467,12 +34467,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>9328</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>22785</t>
+          <t>22703</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -34482,12 +34482,12 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -34508,12 +34508,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>22930</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -34523,12 +34523,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -34543,12 +34543,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>19358</t>
+          <t>18287</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>38059</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -34558,12 +34558,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -34578,12 +34578,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>33229</t>
+          <t>33257</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>56275</t>
+          <t>55635</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -34593,12 +34593,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -34619,12 +34619,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>131285</t>
+          <t>131143</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>151220</t>
+          <t>151357</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -34634,12 +34634,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -34654,12 +34654,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>173590</t>
+          <t>173499</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>197663</t>
+          <t>197886</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -34669,12 +34669,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -34689,12 +34689,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>311417</t>
+          <t>311207</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>342013</t>
+          <t>344436</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -34704,12 +34704,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ19A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ19A-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,229 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,13</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.330489826068714</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>1.13459906763783</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 2,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 1,49</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="n">
+        <v>1.485665829952781</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,34</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,44</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,37</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,14; 1,73</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,15; 1,44</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,18; 1,59</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1,24; 1,91</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,15; 1,45</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,21; 1,61</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,17; 1,8</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1,15; 1,62</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1,18; 1,49</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1,2; 1,45</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 1,58</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 1,61</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.308450890548465</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.254351920529424</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.33824206432701</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.44209565514009</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>1.267310310926557</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1.3626401537738</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1.359568584707309</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1.311579185785568</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1.287293412106561</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>1.301718846454888</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1.347985917676986</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>1.371659602914431</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,75</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.137605032992014</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.15325677241233</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1.183004064926871</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1.235696467554995</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1.151698555219894</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1.206771431776155</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1.174852967454483</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1.150567331618851</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>1.183891515471672</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>1.203512879785854</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>1.230882648661644</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>1.228176654168621</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,37; 1,87</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,5; 2,07</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,28; 1,67</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,18; 1,63</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 2,03</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,48; 2,12</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,39; 1,85</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1,43; 2,23</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1,49; 1,85</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1,56; 1,97</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1,37; 1,66</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,33; 1,69</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.726108496316439</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.442046914629945</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.588825494947312</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.91289214781491</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1.448183673464116</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1.614653188445114</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>1.795289358400867</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>1.615992669842668</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>1.485023090266586</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>1.446063457434674</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>1.576732478432921</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>1.613707931291302</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +881,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,26</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,6</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,62</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,21</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,97</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2,45</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2,23</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1,94</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.571108984483274</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.746349572968261</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.447237211118669</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.329164214130937</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1.742910290804939</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.728205414414572</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1.572819428265267</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1.70907372053742</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1.656281792791204</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1.736727485281704</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>1.509064121457368</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>1.475671825884041</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,91; 2,69</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,95; 3,02</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,31; 2,12</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,42; 1,98</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,22; 3,18</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,82; 2,52</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,84; 2,82</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1,69; 2,35</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2,17; 2,82</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1,98; 2,58</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1,68; 2,37</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 2,06</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.374182619158786</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.495826677943361</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.280976550886487</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.1826355525025</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.505860575709046</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1.481408466552243</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1.386982791287648</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>1.426750105508684</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>1.490810174259845</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>1.559769640995939</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1.367702792812192</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>1.328628036623535</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.872429652250635</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.068397309028274</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.672909443295079</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.632444826645071</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.033605816790689</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2.117173568275923</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1.853409744439545</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2.232536226280792</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>1.850123776895271</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>1.972365572958843</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>1.664026919796127</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>1.689191990221141</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2.2618393525195</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2.338890663422362</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.598100218088795</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.666605144989296</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>2.619323076712202</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>2.129912288540635</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>2.210360403066509</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>1.973138826151274</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>2.448284595247762</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>2.229172132635477</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>1.940422975002927</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>1.818700514940493</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1.912888829262782</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.954681368835527</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1.312527260489902</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1.417879109190046</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>2.224762100234923</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1.822337866114711</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1.839054635435049</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>1.689078815626397</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>2.173300577152002</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1.975744598277648</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1.68135348394829</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>1.60013860164098</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.686576482694611</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.016111988661357</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.123719611211502</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.977965440915588</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>3.178617033487353</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>2.524396855964194</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>2.822946929398247</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>2.345791037435864</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>2.815000137994422</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>2.578773376503532</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>2.37160451956885</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>2.058416085019328</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1,63</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 2,0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,61; 2,03</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,36; 1,69</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1,37; 1,68</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,8; 2,26</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,62; 1,99</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,61; 2,06</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1,59; 2,0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1,75; 2,05</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1,66; 1,94</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 1,79</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 1,76</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.786825818666424</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.782453159258854</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.48086844616021</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.502659336363387</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1.993241561919901</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.777420584992033</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>1.779456636127368</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>1.764156338362921</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1.892420671133467</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>1.779921737372992</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>1.632278737270179</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>1.624855584934637</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1.596937231107316</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1.609879991487878</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.357537641162079</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1.367164256115675</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1.801622482204842</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1.623542336790238</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>1.611469245960365</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>1.587362794801572</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>1.752395683607792</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>1.664851541796112</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>1.519608054587339</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>1.505309389254132</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.001312892169774</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.030666812008528</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.686592356787395</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.68380003308149</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.263751846685783</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1.990088529381051</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>2.062265646559934</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>2.002802040345152</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>2.046604950324058</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>1.935848419508594</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>1.790761545174466</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>1.761780115122304</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1287,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
